--- a/output/yearly_population_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_54_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6330</v>
+        <v>6103</v>
       </c>
       <c r="C2" t="n">
-        <v>8613</v>
+        <v>6789</v>
       </c>
       <c r="D2" t="n">
-        <v>32371</v>
+        <v>26794</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4060</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>4305</v>
+        <v>9258</v>
       </c>
       <c r="D3" t="n">
-        <v>16408</v>
+        <v>12395</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3085</v>
+        <v>2477</v>
       </c>
       <c r="C4" t="n">
-        <v>3286</v>
+        <v>6224</v>
       </c>
       <c r="D4" t="n">
-        <v>7876</v>
+        <v>5939</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1910</v>
+        <v>1653</v>
       </c>
       <c r="C5" t="n">
-        <v>3403</v>
+        <v>4416</v>
       </c>
       <c r="D5" t="n">
-        <v>2833</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1085</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>2680</v>
+        <v>3055</v>
       </c>
       <c r="D6" t="n">
-        <v>1196</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>470</v>
       </c>
       <c r="C7" t="n">
-        <v>1511</v>
+        <v>2081</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>690</v>
+        <v>977</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -926,7 +926,7 @@
         <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8209</v>
+        <v>5955</v>
       </c>
       <c r="C2" t="n">
-        <v>5524</v>
+        <v>6370</v>
       </c>
       <c r="D2" t="n">
-        <v>28048</v>
+        <v>27863</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>3914</v>
       </c>
       <c r="C3" t="n">
-        <v>5539</v>
+        <v>7159</v>
       </c>
       <c r="D3" t="n">
-        <v>17476</v>
+        <v>13520</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3038</v>
+        <v>2561</v>
       </c>
       <c r="C4" t="n">
-        <v>3685</v>
+        <v>7550</v>
       </c>
       <c r="D4" t="n">
-        <v>8953</v>
+        <v>6812</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2136</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="n">
-        <v>3276</v>
+        <v>5114</v>
       </c>
       <c r="D5" t="n">
-        <v>3569</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1317</v>
+        <v>1156</v>
       </c>
       <c r="C6" t="n">
-        <v>2986</v>
+        <v>3639</v>
       </c>
       <c r="D6" t="n">
-        <v>1419</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>705</v>
+        <v>621</v>
       </c>
       <c r="C7" t="n">
-        <v>2022</v>
+        <v>2489</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>1051</v>
+        <v>1452</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>623</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
+        <v>282</v>
+      </c>
+      <c r="D10" t="n">
         <v>250</v>
-      </c>
-      <c r="D10" t="n">
-        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9321</v>
+        <v>7372</v>
       </c>
       <c r="C2" t="n">
-        <v>8871</v>
+        <v>8425</v>
       </c>
       <c r="D2" t="n">
-        <v>26641</v>
+        <v>35946</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4717</v>
+        <v>3877</v>
       </c>
       <c r="C3" t="n">
-        <v>4895</v>
+        <v>6073</v>
       </c>
       <c r="D3" t="n">
-        <v>17682</v>
+        <v>14375</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2983</v>
+        <v>2641</v>
       </c>
       <c r="C4" t="n">
-        <v>4409</v>
+        <v>7151</v>
       </c>
       <c r="D4" t="n">
-        <v>9989</v>
+        <v>7505</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2226</v>
+        <v>1873</v>
       </c>
       <c r="C5" t="n">
-        <v>3388</v>
+        <v>5987</v>
       </c>
       <c r="D5" t="n">
-        <v>4201</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1521</v>
+        <v>1279</v>
       </c>
       <c r="C6" t="n">
-        <v>3051</v>
+        <v>4215</v>
       </c>
       <c r="D6" t="n">
-        <v>1695</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>855</v>
+        <v>747</v>
       </c>
       <c r="C7" t="n">
-        <v>2427</v>
+        <v>2925</v>
       </c>
       <c r="D7" t="n">
-        <v>832</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>411</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
-        <v>1430</v>
+        <v>1857</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>692</v>
+        <v>925</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>6764</v>
       </c>
       <c r="C2" t="n">
-        <v>5890</v>
+        <v>5796</v>
       </c>
       <c r="D2" t="n">
-        <v>21778</v>
+        <v>29446</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5595</v>
+        <v>4694</v>
       </c>
       <c r="C3" t="n">
-        <v>7641</v>
+        <v>9725</v>
       </c>
       <c r="D3" t="n">
-        <v>19481</v>
+        <v>15415</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2056</v>
+        <v>1730</v>
       </c>
       <c r="C4" t="n">
-        <v>5749</v>
+        <v>9660</v>
       </c>
       <c r="D4" t="n">
-        <v>9480</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1405</v>
+        <v>1181</v>
       </c>
       <c r="C5" t="n">
-        <v>2989</v>
+        <v>4130</v>
       </c>
       <c r="D5" t="n">
-        <v>2830</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>2378</v>
+        <v>2866</v>
       </c>
       <c r="D6" t="n">
-        <v>815</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1401</v>
+        <v>1819</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>678</v>
+        <v>906</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>393</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>78</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5102</v>
+        <v>4233</v>
       </c>
       <c r="C2" t="n">
-        <v>3344</v>
+        <v>3879</v>
       </c>
       <c r="D2" t="n">
-        <v>15574</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5864</v>
+        <v>4804</v>
       </c>
       <c r="C3" t="n">
-        <v>6165</v>
+        <v>7219</v>
       </c>
       <c r="D3" t="n">
-        <v>18845</v>
+        <v>16583</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2964</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>6758</v>
+        <v>9767</v>
       </c>
       <c r="D4" t="n">
-        <v>10909</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1571</v>
+        <v>1317</v>
       </c>
       <c r="C5" t="n">
-        <v>4236</v>
+        <v>6525</v>
       </c>
       <c r="D5" t="n">
-        <v>3628</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>812</v>
       </c>
       <c r="C6" t="n">
-        <v>2716</v>
+        <v>3477</v>
       </c>
       <c r="D6" t="n">
-        <v>1022</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>1801</v>
+        <v>2237</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>904</v>
+        <v>1195</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
         <v>259</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5788</v>
+        <v>4025</v>
       </c>
       <c r="C2" t="n">
-        <v>5135</v>
+        <v>8034</v>
       </c>
       <c r="D2" t="n">
-        <v>20450</v>
+        <v>17529</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4643</v>
+        <v>3837</v>
       </c>
       <c r="C3" t="n">
-        <v>4199</v>
+        <v>5009</v>
       </c>
       <c r="D3" t="n">
-        <v>17077</v>
+        <v>16136</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3663</v>
+        <v>2959</v>
       </c>
       <c r="C4" t="n">
-        <v>6380</v>
+        <v>8316</v>
       </c>
       <c r="D4" t="n">
-        <v>11948</v>
+        <v>9309</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>1597</v>
       </c>
       <c r="C5" t="n">
-        <v>5358</v>
+        <v>7976</v>
       </c>
       <c r="D5" t="n">
-        <v>4705</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1114</v>
+        <v>948</v>
       </c>
       <c r="C6" t="n">
-        <v>3415</v>
+        <v>4789</v>
       </c>
       <c r="D6" t="n">
-        <v>1408</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>2203</v>
+        <v>2792</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>1290</v>
+        <v>1624</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>724</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3409</v>
+        <v>2389</v>
       </c>
       <c r="C2" t="n">
-        <v>2306</v>
+        <v>3778</v>
       </c>
       <c r="D2" t="n">
-        <v>14098</v>
+        <v>12224</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4751</v>
+        <v>3777</v>
       </c>
       <c r="C3" t="n">
-        <v>4387</v>
+        <v>5873</v>
       </c>
       <c r="D3" t="n">
-        <v>17044</v>
+        <v>15919</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4052</v>
+        <v>3241</v>
       </c>
       <c r="C4" t="n">
-        <v>6167</v>
+        <v>7861</v>
       </c>
       <c r="D4" t="n">
-        <v>12650</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2006</v>
+        <v>1671</v>
       </c>
       <c r="C5" t="n">
-        <v>6326</v>
+        <v>9312</v>
       </c>
       <c r="D5" t="n">
-        <v>5113</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>794</v>
       </c>
       <c r="C6" t="n">
-        <v>4242</v>
+        <v>5697</v>
       </c>
       <c r="D6" t="n">
-        <v>1380</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>2336</v>
+        <v>2931</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>997</v>
+        <v>1202</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3847</v>
+        <v>2666</v>
       </c>
       <c r="C2" t="n">
-        <v>2675</v>
+        <v>7833</v>
       </c>
       <c r="D2" t="n">
-        <v>18325</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>2746</v>
       </c>
       <c r="C3" t="n">
-        <v>3022</v>
+        <v>4386</v>
       </c>
       <c r="D3" t="n">
-        <v>15497</v>
+        <v>14499</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3794</v>
+        <v>3049</v>
       </c>
       <c r="C4" t="n">
-        <v>5226</v>
+        <v>6837</v>
       </c>
       <c r="D4" t="n">
-        <v>12982</v>
+        <v>10683</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2519</v>
+        <v>2031</v>
       </c>
       <c r="C5" t="n">
-        <v>6181</v>
+        <v>8477</v>
       </c>
       <c r="D5" t="n">
-        <v>6115</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>1014</v>
       </c>
       <c r="C6" t="n">
-        <v>5143</v>
+        <v>7283</v>
       </c>
       <c r="D6" t="n">
-        <v>1912</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="C7" t="n">
-        <v>3165</v>
+        <v>4042</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1514</v>
+        <v>1863</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>587</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2746</v>
+        <v>1859</v>
       </c>
       <c r="C2" t="n">
-        <v>1659</v>
+        <v>4366</v>
       </c>
       <c r="D2" t="n">
-        <v>14372</v>
+        <v>8104</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3209</v>
+        <v>2384</v>
       </c>
       <c r="C3" t="n">
-        <v>2609</v>
+        <v>5199</v>
       </c>
       <c r="D3" t="n">
-        <v>14993</v>
+        <v>13427</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3431</v>
+        <v>2728</v>
       </c>
       <c r="C4" t="n">
-        <v>4336</v>
+        <v>5903</v>
       </c>
       <c r="D4" t="n">
-        <v>13049</v>
+        <v>10937</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2777</v>
+        <v>2222</v>
       </c>
       <c r="C5" t="n">
-        <v>5932</v>
+        <v>8043</v>
       </c>
       <c r="D5" t="n">
-        <v>6837</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1477</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="n">
-        <v>5687</v>
+        <v>7947</v>
       </c>
       <c r="D6" t="n">
-        <v>2289</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>3884</v>
+        <v>5040</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1937</v>
+        <v>2415</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4438</v>
+        <v>3813</v>
       </c>
       <c r="C2" t="n">
-        <v>9884</v>
+        <v>5533</v>
       </c>
       <c r="D2" t="n">
-        <v>17714</v>
+        <v>10488</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2557</v>
+        <v>1855</v>
       </c>
       <c r="C3" t="n">
-        <v>1963</v>
+        <v>4331</v>
       </c>
       <c r="D3" t="n">
-        <v>14073</v>
+        <v>11928</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2911</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>3483</v>
+        <v>5482</v>
       </c>
       <c r="D4" t="n">
-        <v>12806</v>
+        <v>10963</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2767</v>
+        <v>2183</v>
       </c>
       <c r="C5" t="n">
-        <v>5134</v>
+        <v>7012</v>
       </c>
       <c r="D5" t="n">
-        <v>7523</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1776</v>
+        <v>1424</v>
       </c>
       <c r="C6" t="n">
-        <v>5735</v>
+        <v>7917</v>
       </c>
       <c r="D6" t="n">
-        <v>2870</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>654</v>
+        <v>497</v>
       </c>
       <c r="C7" t="n">
-        <v>4627</v>
+        <v>6169</v>
       </c>
       <c r="D7" t="n">
-        <v>964</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>2642</v>
+        <v>3314</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1082</v>
+        <v>1238</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>5249</v>
       </c>
       <c r="C2" t="n">
-        <v>3571</v>
+        <v>6662</v>
       </c>
       <c r="D2" t="n">
-        <v>12978</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3143</v>
+        <v>2755</v>
       </c>
       <c r="C2" t="n">
-        <v>5536</v>
+        <v>3187</v>
       </c>
       <c r="D2" t="n">
-        <v>13037</v>
+        <v>7803</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3497</v>
+        <v>2619</v>
       </c>
       <c r="C3" t="n">
-        <v>4030</v>
+        <v>4981</v>
       </c>
       <c r="D3" t="n">
-        <v>15381</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4041</v>
+        <v>3174</v>
       </c>
       <c r="C4" t="n">
-        <v>5097</v>
+        <v>7899</v>
       </c>
       <c r="D4" t="n">
-        <v>13289</v>
+        <v>11166</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1743</v>
+        <v>1356</v>
       </c>
       <c r="C5" t="n">
-        <v>7784</v>
+        <v>10794</v>
       </c>
       <c r="D5" t="n">
-        <v>6895</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>604</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>5770</v>
+        <v>7519</v>
       </c>
       <c r="D6" t="n">
-        <v>2218</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>2589</v>
+        <v>3247</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1060</v>
+        <v>1213</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4515,10 +4515,10 @@
         <v>7129</v>
       </c>
       <c r="C2" t="n">
-        <v>7556</v>
+        <v>8437</v>
       </c>
       <c r="D2" t="n">
-        <v>16627</v>
+        <v>9108</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2967</v>
+        <v>2231</v>
       </c>
       <c r="C3" t="n">
-        <v>1799</v>
+        <v>3410</v>
       </c>
       <c r="D3" t="n">
-        <v>2819</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4839</v>
+        <v>4705</v>
       </c>
       <c r="C2" t="n">
-        <v>3543</v>
+        <v>7569</v>
       </c>
       <c r="D2" t="n">
-        <v>15592</v>
+        <v>18303</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4147</v>
+        <v>3840</v>
       </c>
       <c r="C3" t="n">
-        <v>4360</v>
+        <v>5428</v>
       </c>
       <c r="D3" t="n">
-        <v>4931</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1322</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="n">
-        <v>1098</v>
+        <v>2073</v>
       </c>
       <c r="D4" t="n">
-        <v>1749</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4606</v>
+        <v>3975</v>
       </c>
       <c r="C2" t="n">
-        <v>7808</v>
+        <v>5182</v>
       </c>
       <c r="D2" t="n">
-        <v>19572</v>
+        <v>23472</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3698</v>
+        <v>3512</v>
       </c>
       <c r="C3" t="n">
-        <v>3388</v>
+        <v>5709</v>
       </c>
       <c r="D3" t="n">
-        <v>6281</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2316</v>
+        <v>2047</v>
       </c>
       <c r="C4" t="n">
-        <v>2922</v>
+        <v>3930</v>
       </c>
       <c r="D4" t="n">
-        <v>2306</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>603</v>
+        <v>472</v>
       </c>
       <c r="C5" t="n">
-        <v>694</v>
+        <v>1229</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6123</v>
+        <v>5366</v>
       </c>
       <c r="C2" t="n">
-        <v>5746</v>
+        <v>4851</v>
       </c>
       <c r="D2" t="n">
-        <v>32897</v>
+        <v>21916</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3401</v>
+        <v>3080</v>
       </c>
       <c r="C3" t="n">
-        <v>4991</v>
+        <v>4733</v>
       </c>
       <c r="D3" t="n">
-        <v>7859</v>
+        <v>7457</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2546</v>
+        <v>2365</v>
       </c>
       <c r="C4" t="n">
-        <v>3083</v>
+        <v>4804</v>
       </c>
       <c r="D4" t="n">
-        <v>2938</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1219</v>
+        <v>1029</v>
       </c>
       <c r="C5" t="n">
-        <v>1855</v>
+        <v>2591</v>
       </c>
       <c r="D5" t="n">
-        <v>1397</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>498</v>
+        <v>769</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6674</v>
+        <v>5625</v>
       </c>
       <c r="C2" t="n">
-        <v>3871</v>
+        <v>10661</v>
       </c>
       <c r="D2" t="n">
-        <v>38728</v>
+        <v>21586</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3474</v>
+        <v>3041</v>
       </c>
       <c r="C3" t="n">
-        <v>4404</v>
+        <v>3926</v>
       </c>
       <c r="D3" t="n">
-        <v>10452</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1835</v>
+        <v>1681</v>
       </c>
       <c r="C4" t="n">
-        <v>3364</v>
+        <v>3866</v>
       </c>
       <c r="D4" t="n">
-        <v>3243</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>985</v>
+        <v>883</v>
       </c>
       <c r="C5" t="n">
-        <v>1829</v>
+        <v>2750</v>
       </c>
       <c r="D5" t="n">
-        <v>1326</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>367</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>792</v>
+        <v>1136</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6729</v>
+        <v>4803</v>
       </c>
       <c r="C2" t="n">
-        <v>3888</v>
+        <v>9452</v>
       </c>
       <c r="D2" t="n">
-        <v>27130</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4220</v>
+        <v>3602</v>
       </c>
       <c r="C3" t="n">
-        <v>3503</v>
+        <v>6815</v>
       </c>
       <c r="D3" t="n">
-        <v>14642</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2334</v>
+        <v>2074</v>
       </c>
       <c r="C4" t="n">
-        <v>3933</v>
+        <v>3822</v>
       </c>
       <c r="D4" t="n">
-        <v>4666</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="n">
-        <v>2704</v>
+        <v>3357</v>
       </c>
       <c r="D5" t="n">
-        <v>1672</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>631</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>1379</v>
+        <v>2051</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>567</v>
+        <v>798</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5422</v>
+        <v>5688</v>
       </c>
       <c r="C2" t="n">
-        <v>6632</v>
+        <v>14030</v>
       </c>
       <c r="D2" t="n">
-        <v>28218</v>
+        <v>20970</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4489</v>
+        <v>3447</v>
       </c>
       <c r="C3" t="n">
-        <v>3211</v>
+        <v>7143</v>
       </c>
       <c r="D3" t="n">
-        <v>15585</v>
+        <v>11697</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2831</v>
+        <v>2422</v>
       </c>
       <c r="C4" t="n">
-        <v>3603</v>
+        <v>5437</v>
       </c>
       <c r="D4" t="n">
-        <v>6394</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1567</v>
+        <v>1415</v>
       </c>
       <c r="C5" t="n">
-        <v>3332</v>
+        <v>3509</v>
       </c>
       <c r="D5" t="n">
-        <v>2196</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>2075</v>
+        <v>2729</v>
       </c>
       <c r="D6" t="n">
-        <v>1004</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>990</v>
+        <v>1460</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>414</v>
+        <v>550</v>
       </c>
       <c r="D8" t="n">
         <v>412</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_54_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6103</v>
+        <v>6316</v>
       </c>
       <c r="C2" t="n">
-        <v>6789</v>
+        <v>11533</v>
       </c>
       <c r="D2" t="n">
-        <v>26794</v>
+        <v>23364</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>4167</v>
       </c>
       <c r="C3" t="n">
-        <v>9258</v>
+        <v>5669</v>
       </c>
       <c r="D3" t="n">
-        <v>12395</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2477</v>
+        <v>3398</v>
       </c>
       <c r="C4" t="n">
-        <v>6224</v>
+        <v>4654</v>
       </c>
       <c r="D4" t="n">
-        <v>5939</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>2063</v>
       </c>
       <c r="C5" t="n">
-        <v>4416</v>
+        <v>4797</v>
       </c>
       <c r="D5" t="n">
-        <v>2284</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>1127</v>
       </c>
       <c r="C6" t="n">
-        <v>3055</v>
+        <v>3699</v>
       </c>
       <c r="D6" t="n">
-        <v>1022</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>470</v>
+        <v>531</v>
       </c>
       <c r="C7" t="n">
-        <v>2081</v>
+        <v>2457</v>
       </c>
       <c r="D7" t="n">
-        <v>632</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>977</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>472</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5955</v>
+        <v>6641</v>
       </c>
       <c r="C2" t="n">
-        <v>6370</v>
+        <v>14785</v>
       </c>
       <c r="D2" t="n">
-        <v>27863</v>
+        <v>22322</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3914</v>
+        <v>4151</v>
       </c>
       <c r="C3" t="n">
-        <v>7159</v>
+        <v>7258</v>
       </c>
       <c r="D3" t="n">
-        <v>13520</v>
+        <v>13528</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2561</v>
+        <v>3186</v>
       </c>
       <c r="C4" t="n">
-        <v>7550</v>
+        <v>4980</v>
       </c>
       <c r="D4" t="n">
-        <v>6812</v>
+        <v>7113</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1775</v>
+        <v>2330</v>
       </c>
       <c r="C5" t="n">
-        <v>5114</v>
+        <v>4632</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1156</v>
+        <v>1371</v>
       </c>
       <c r="C6" t="n">
-        <v>3639</v>
+        <v>4102</v>
       </c>
       <c r="D6" t="n">
-        <v>1202</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>621</v>
+        <v>693</v>
       </c>
       <c r="C7" t="n">
-        <v>2489</v>
+        <v>2991</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="C8" t="n">
-        <v>1452</v>
+        <v>1718</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>773</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7372</v>
+        <v>7450</v>
       </c>
       <c r="C2" t="n">
-        <v>8425</v>
+        <v>16220</v>
       </c>
       <c r="D2" t="n">
-        <v>35946</v>
+        <v>24056</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3877</v>
+        <v>4176</v>
       </c>
       <c r="C3" t="n">
-        <v>6073</v>
+        <v>9106</v>
       </c>
       <c r="D3" t="n">
-        <v>14375</v>
+        <v>13717</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2641</v>
+        <v>3037</v>
       </c>
       <c r="C4" t="n">
-        <v>7151</v>
+        <v>5838</v>
       </c>
       <c r="D4" t="n">
-        <v>7505</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1873</v>
+        <v>2370</v>
       </c>
       <c r="C5" t="n">
-        <v>5987</v>
+        <v>4631</v>
       </c>
       <c r="D5" t="n">
-        <v>3254</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1279</v>
+        <v>1580</v>
       </c>
       <c r="C6" t="n">
-        <v>4215</v>
+        <v>4235</v>
       </c>
       <c r="D6" t="n">
-        <v>1383</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>747</v>
+        <v>853</v>
       </c>
       <c r="C7" t="n">
-        <v>2925</v>
+        <v>3425</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="C8" t="n">
-        <v>1857</v>
+        <v>2174</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C9" t="n">
-        <v>925</v>
+        <v>1107</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>402</v>
+        <v>476</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6764</v>
+        <v>6930</v>
       </c>
       <c r="C2" t="n">
-        <v>5796</v>
+        <v>11289</v>
       </c>
       <c r="D2" t="n">
-        <v>29446</v>
+        <v>19903</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4694</v>
+        <v>5184</v>
       </c>
       <c r="C3" t="n">
-        <v>9725</v>
+        <v>12894</v>
       </c>
       <c r="D3" t="n">
-        <v>15415</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1730</v>
+        <v>2189</v>
       </c>
       <c r="C4" t="n">
-        <v>9660</v>
+        <v>7584</v>
       </c>
       <c r="D4" t="n">
-        <v>7148</v>
+        <v>7460</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1181</v>
+        <v>1459</v>
       </c>
       <c r="C5" t="n">
-        <v>4130</v>
+        <v>4150</v>
       </c>
       <c r="D5" t="n">
-        <v>2230</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>788</v>
       </c>
       <c r="C6" t="n">
-        <v>2866</v>
+        <v>3356</v>
       </c>
       <c r="D6" t="n">
-        <v>719</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="C7" t="n">
-        <v>1819</v>
+        <v>2130</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>906</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4233</v>
+        <v>4445</v>
       </c>
       <c r="C2" t="n">
-        <v>3879</v>
+        <v>5236</v>
       </c>
       <c r="D2" t="n">
-        <v>21495</v>
+        <v>13630</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4804</v>
+        <v>5121</v>
       </c>
       <c r="C3" t="n">
-        <v>7219</v>
+        <v>11076</v>
       </c>
       <c r="D3" t="n">
-        <v>16583</v>
+        <v>14875</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>2874</v>
       </c>
       <c r="C4" t="n">
-        <v>9767</v>
+        <v>10113</v>
       </c>
       <c r="D4" t="n">
-        <v>8189</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1317</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="n">
-        <v>6525</v>
+        <v>5574</v>
       </c>
       <c r="D5" t="n">
-        <v>2818</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>812</v>
+        <v>929</v>
       </c>
       <c r="C6" t="n">
-        <v>3477</v>
+        <v>3828</v>
       </c>
       <c r="D6" t="n">
-        <v>876</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>2237</v>
+        <v>2608</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>1416</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>499</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4025</v>
+        <v>4186</v>
       </c>
       <c r="C2" t="n">
-        <v>8034</v>
+        <v>8772</v>
       </c>
       <c r="D2" t="n">
-        <v>17529</v>
+        <v>18334</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3837</v>
+        <v>4075</v>
       </c>
       <c r="C3" t="n">
-        <v>5009</v>
+        <v>7410</v>
       </c>
       <c r="D3" t="n">
-        <v>16136</v>
+        <v>13706</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2959</v>
+        <v>3263</v>
       </c>
       <c r="C4" t="n">
-        <v>8316</v>
+        <v>10461</v>
       </c>
       <c r="D4" t="n">
-        <v>9309</v>
+        <v>9182</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="C5" t="n">
-        <v>7976</v>
+        <v>7506</v>
       </c>
       <c r="D5" t="n">
-        <v>3557</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>1120</v>
       </c>
       <c r="C6" t="n">
-        <v>4789</v>
+        <v>4546</v>
       </c>
       <c r="D6" t="n">
-        <v>1144</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>2792</v>
+        <v>3146</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>1624</v>
+        <v>1896</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>836</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2389</v>
+        <v>2563</v>
       </c>
       <c r="C2" t="n">
-        <v>3778</v>
+        <v>4269</v>
       </c>
       <c r="D2" t="n">
-        <v>12224</v>
+        <v>12786</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3777</v>
+        <v>3959</v>
       </c>
       <c r="C3" t="n">
-        <v>5873</v>
+        <v>7644</v>
       </c>
       <c r="D3" t="n">
-        <v>15919</v>
+        <v>13880</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3241</v>
+        <v>3585</v>
       </c>
       <c r="C4" t="n">
-        <v>7861</v>
+        <v>10310</v>
       </c>
       <c r="D4" t="n">
-        <v>10096</v>
+        <v>9770</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>1967</v>
       </c>
       <c r="C5" t="n">
-        <v>9312</v>
+        <v>9237</v>
       </c>
       <c r="D5" t="n">
-        <v>3771</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>794</v>
+        <v>896</v>
       </c>
       <c r="C6" t="n">
-        <v>5697</v>
+        <v>5479</v>
       </c>
       <c r="D6" t="n">
-        <v>1133</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>2931</v>
+        <v>3335</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1202</v>
+        <v>1376</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2666</v>
+        <v>3216</v>
       </c>
       <c r="C2" t="n">
-        <v>7833</v>
+        <v>10738</v>
       </c>
       <c r="D2" t="n">
-        <v>10980</v>
+        <v>16141</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2746</v>
+        <v>2911</v>
       </c>
       <c r="C3" t="n">
-        <v>4386</v>
+        <v>5489</v>
       </c>
       <c r="D3" t="n">
-        <v>14499</v>
+        <v>12829</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3049</v>
+        <v>3297</v>
       </c>
       <c r="C4" t="n">
-        <v>6837</v>
+        <v>8966</v>
       </c>
       <c r="D4" t="n">
-        <v>10683</v>
+        <v>10104</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2031</v>
+        <v>2310</v>
       </c>
       <c r="C5" t="n">
-        <v>8477</v>
+        <v>9597</v>
       </c>
       <c r="D5" t="n">
-        <v>4567</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>7283</v>
+        <v>6999</v>
       </c>
       <c r="D6" t="n">
-        <v>1472</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>4042</v>
+        <v>4218</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1863</v>
+        <v>2074</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>646</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1859</v>
+        <v>2456</v>
       </c>
       <c r="C2" t="n">
-        <v>4366</v>
+        <v>6526</v>
       </c>
       <c r="D2" t="n">
-        <v>8104</v>
+        <v>11421</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2384</v>
+        <v>2634</v>
       </c>
       <c r="C3" t="n">
-        <v>5199</v>
+        <v>6855</v>
       </c>
       <c r="D3" t="n">
-        <v>13427</v>
+        <v>12522</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2728</v>
+        <v>2913</v>
       </c>
       <c r="C4" t="n">
-        <v>5903</v>
+        <v>7616</v>
       </c>
       <c r="D4" t="n">
-        <v>10937</v>
+        <v>10233</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2222</v>
+        <v>2489</v>
       </c>
       <c r="C5" t="n">
-        <v>8043</v>
+        <v>9547</v>
       </c>
       <c r="D5" t="n">
-        <v>5117</v>
+        <v>5176</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1184</v>
+        <v>1334</v>
       </c>
       <c r="C6" t="n">
-        <v>7947</v>
+        <v>8045</v>
       </c>
       <c r="D6" t="n">
-        <v>1765</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>5040</v>
+        <v>5132</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2415</v>
+        <v>2588</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3813</v>
+        <v>3710</v>
       </c>
       <c r="C2" t="n">
-        <v>5533</v>
+        <v>5823</v>
       </c>
       <c r="D2" t="n">
-        <v>10488</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1855</v>
+        <v>2168</v>
       </c>
       <c r="C3" t="n">
-        <v>4331</v>
+        <v>6009</v>
       </c>
       <c r="D3" t="n">
-        <v>11928</v>
+        <v>11617</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>2450</v>
       </c>
       <c r="C4" t="n">
-        <v>5482</v>
+        <v>7150</v>
       </c>
       <c r="D4" t="n">
-        <v>10963</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2183</v>
+        <v>2427</v>
       </c>
       <c r="C5" t="n">
-        <v>7012</v>
+        <v>8606</v>
       </c>
       <c r="D5" t="n">
-        <v>5743</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="C6" t="n">
-        <v>7917</v>
+        <v>8528</v>
       </c>
       <c r="D6" t="n">
-        <v>2160</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="C7" t="n">
-        <v>6169</v>
+        <v>6157</v>
       </c>
       <c r="D7" t="n">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3314</v>
+        <v>3459</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1238</v>
+        <v>1277</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5249</v>
+        <v>7163</v>
       </c>
       <c r="C2" t="n">
-        <v>6662</v>
+        <v>11975</v>
       </c>
       <c r="D2" t="n">
-        <v>5149</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2755</v>
+        <v>2711</v>
       </c>
       <c r="C2" t="n">
-        <v>3187</v>
+        <v>3447</v>
       </c>
       <c r="D2" t="n">
-        <v>7803</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2619</v>
+        <v>2928</v>
       </c>
       <c r="C3" t="n">
-        <v>4981</v>
+        <v>6586</v>
       </c>
       <c r="D3" t="n">
-        <v>12774</v>
+        <v>12723</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3174</v>
+        <v>3493</v>
       </c>
       <c r="C4" t="n">
-        <v>7899</v>
+        <v>10148</v>
       </c>
       <c r="D4" t="n">
-        <v>11166</v>
+        <v>10378</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>1469</v>
       </c>
       <c r="C5" t="n">
-        <v>10794</v>
+        <v>12223</v>
       </c>
       <c r="D5" t="n">
-        <v>5193</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="6">
@@ -4257,10 +4257,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="C6" t="n">
-        <v>7519</v>
+        <v>7538</v>
       </c>
       <c r="D6" t="n">
         <v>1753</v>
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3247</v>
+        <v>3389</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1213</v>
+        <v>1251</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7129</v>
+        <v>7473</v>
       </c>
       <c r="C2" t="n">
-        <v>8437</v>
+        <v>10744</v>
       </c>
       <c r="D2" t="n">
-        <v>9108</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2231</v>
+        <v>3042</v>
       </c>
       <c r="C3" t="n">
-        <v>3410</v>
+        <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>1545</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4705</v>
+        <v>5348</v>
       </c>
       <c r="C2" t="n">
-        <v>7569</v>
+        <v>4819</v>
       </c>
       <c r="D2" t="n">
-        <v>18303</v>
+        <v>18483</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3840</v>
+        <v>4318</v>
       </c>
       <c r="C3" t="n">
-        <v>5428</v>
+        <v>7502</v>
       </c>
       <c r="D3" t="n">
-        <v>2701</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1003</v>
+        <v>1356</v>
       </c>
       <c r="C4" t="n">
-        <v>2073</v>
+        <v>3580</v>
       </c>
       <c r="D4" t="n">
-        <v>1492</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3975</v>
+        <v>5524</v>
       </c>
       <c r="C2" t="n">
-        <v>5182</v>
+        <v>5920</v>
       </c>
       <c r="D2" t="n">
-        <v>23472</v>
+        <v>18958</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3512</v>
+        <v>3966</v>
       </c>
       <c r="C3" t="n">
-        <v>5709</v>
+        <v>5260</v>
       </c>
       <c r="D3" t="n">
-        <v>5002</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2047</v>
+        <v>2378</v>
       </c>
       <c r="C4" t="n">
-        <v>3930</v>
+        <v>5689</v>
       </c>
       <c r="D4" t="n">
-        <v>1678</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>472</v>
+        <v>606</v>
       </c>
       <c r="C5" t="n">
-        <v>1229</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="n">
-        <v>1194</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
         <v>177</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5366</v>
+        <v>6849</v>
       </c>
       <c r="C2" t="n">
-        <v>4851</v>
+        <v>10013</v>
       </c>
       <c r="D2" t="n">
-        <v>21916</v>
+        <v>27222</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3080</v>
+        <v>3857</v>
       </c>
       <c r="C3" t="n">
-        <v>4733</v>
+        <v>4877</v>
       </c>
       <c r="D3" t="n">
-        <v>7457</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2365</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>4804</v>
+        <v>5344</v>
       </c>
       <c r="D4" t="n">
-        <v>2233</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1029</v>
+        <v>1210</v>
       </c>
       <c r="C5" t="n">
-        <v>2591</v>
+        <v>3825</v>
       </c>
       <c r="D5" t="n">
-        <v>1229</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>319</v>
       </c>
       <c r="C6" t="n">
-        <v>769</v>
+        <v>1159</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5625</v>
+        <v>8194</v>
       </c>
       <c r="C2" t="n">
-        <v>10661</v>
+        <v>6977</v>
       </c>
       <c r="D2" t="n">
-        <v>21586</v>
+        <v>23601</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3041</v>
+        <v>3825</v>
       </c>
       <c r="C3" t="n">
-        <v>3926</v>
+        <v>6149</v>
       </c>
       <c r="D3" t="n">
-        <v>8589</v>
+        <v>9373</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1681</v>
+        <v>2007</v>
       </c>
       <c r="C4" t="n">
-        <v>3866</v>
+        <v>4123</v>
       </c>
       <c r="D4" t="n">
-        <v>2721</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>883</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="n">
-        <v>2750</v>
+        <v>3350</v>
       </c>
       <c r="D5" t="n">
-        <v>1096</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="C6" t="n">
-        <v>1136</v>
+        <v>1641</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>472</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4803</v>
+        <v>6867</v>
       </c>
       <c r="C2" t="n">
-        <v>9452</v>
+        <v>4084</v>
       </c>
       <c r="D2" t="n">
-        <v>24005</v>
+        <v>23294</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>4972</v>
       </c>
       <c r="C3" t="n">
-        <v>6815</v>
+        <v>5703</v>
       </c>
       <c r="D3" t="n">
-        <v>10230</v>
+        <v>11073</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2074</v>
+        <v>2549</v>
       </c>
       <c r="C4" t="n">
-        <v>3822</v>
+        <v>5243</v>
       </c>
       <c r="D4" t="n">
-        <v>3877</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1138</v>
+        <v>1342</v>
       </c>
       <c r="C5" t="n">
-        <v>3357</v>
+        <v>3725</v>
       </c>
       <c r="D5" t="n">
-        <v>1390</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556</v>
+        <v>622</v>
       </c>
       <c r="C6" t="n">
-        <v>2051</v>
+        <v>2572</v>
       </c>
       <c r="D6" t="n">
-        <v>803</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>798</v>
+        <v>1108</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5688</v>
+        <v>5281</v>
       </c>
       <c r="C2" t="n">
-        <v>14030</v>
+        <v>8885</v>
       </c>
       <c r="D2" t="n">
-        <v>20970</v>
+        <v>24330</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3447</v>
+        <v>4839</v>
       </c>
       <c r="C3" t="n">
-        <v>7143</v>
+        <v>4216</v>
       </c>
       <c r="D3" t="n">
-        <v>11697</v>
+        <v>12151</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2422</v>
+        <v>3206</v>
       </c>
       <c r="C4" t="n">
-        <v>5437</v>
+        <v>5335</v>
       </c>
       <c r="D4" t="n">
-        <v>4978</v>
+        <v>5312</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1415</v>
+        <v>1681</v>
       </c>
       <c r="C5" t="n">
-        <v>3509</v>
+        <v>4463</v>
       </c>
       <c r="D5" t="n">
-        <v>1788</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>2729</v>
+        <v>3140</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>1460</v>
+        <v>1853</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>550</v>
+        <v>720</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_54_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6316</v>
+        <v>2067</v>
       </c>
       <c r="C2" t="n">
-        <v>11533</v>
+        <v>3476</v>
       </c>
       <c r="D2" t="n">
-        <v>23364</v>
+        <v>15300</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4167</v>
+        <v>3254</v>
       </c>
       <c r="C3" t="n">
-        <v>5669</v>
+        <v>7394</v>
       </c>
       <c r="D3" t="n">
-        <v>13068</v>
+        <v>17294</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3398</v>
+        <v>2148</v>
       </c>
       <c r="C4" t="n">
-        <v>4654</v>
+        <v>6566</v>
       </c>
       <c r="D4" t="n">
-        <v>6332</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2063</v>
+        <v>1192</v>
       </c>
       <c r="C5" t="n">
-        <v>4797</v>
+        <v>3289</v>
       </c>
       <c r="D5" t="n">
-        <v>2450</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>3699</v>
+        <v>1314</v>
       </c>
       <c r="D6" t="n">
-        <v>1100</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>2457</v>
+        <v>569</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1223</v>
+        <v>340</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>472</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6641</v>
+        <v>2343</v>
       </c>
       <c r="C2" t="n">
-        <v>14785</v>
+        <v>5325</v>
       </c>
       <c r="D2" t="n">
-        <v>22322</v>
+        <v>20388</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4151</v>
+        <v>2290</v>
       </c>
       <c r="C3" t="n">
-        <v>7258</v>
+        <v>4665</v>
       </c>
       <c r="D3" t="n">
-        <v>13528</v>
+        <v>15773</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3186</v>
+        <v>2318</v>
       </c>
       <c r="C4" t="n">
-        <v>4980</v>
+        <v>6882</v>
       </c>
       <c r="D4" t="n">
-        <v>7113</v>
+        <v>9229</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2330</v>
+        <v>1447</v>
       </c>
       <c r="C5" t="n">
-        <v>4632</v>
+        <v>4982</v>
       </c>
       <c r="D5" t="n">
-        <v>2971</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1371</v>
+        <v>720</v>
       </c>
       <c r="C6" t="n">
-        <v>4102</v>
+        <v>2298</v>
       </c>
       <c r="D6" t="n">
-        <v>1269</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>693</v>
+        <v>238</v>
       </c>
       <c r="C7" t="n">
-        <v>2991</v>
+        <v>932</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1718</v>
+        <v>446</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>773</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7450</v>
+        <v>1247</v>
       </c>
       <c r="C2" t="n">
-        <v>16220</v>
+        <v>2198</v>
       </c>
       <c r="D2" t="n">
-        <v>24056</v>
+        <v>13735</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4176</v>
+        <v>2217</v>
       </c>
       <c r="C3" t="n">
-        <v>9106</v>
+        <v>4729</v>
       </c>
       <c r="D3" t="n">
-        <v>13717</v>
+        <v>15934</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3037</v>
+        <v>2546</v>
       </c>
       <c r="C4" t="n">
-        <v>5838</v>
+        <v>6592</v>
       </c>
       <c r="D4" t="n">
-        <v>7820</v>
+        <v>10233</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2370</v>
+        <v>1475</v>
       </c>
       <c r="C5" t="n">
-        <v>4631</v>
+        <v>6106</v>
       </c>
       <c r="D5" t="n">
-        <v>3408</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1580</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>4235</v>
+        <v>3024</v>
       </c>
       <c r="D6" t="n">
-        <v>1468</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>853</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>3425</v>
+        <v>946</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>389</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2174</v>
+        <v>462</v>
       </c>
       <c r="D8" t="n">
-        <v>472</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1107</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>476</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6930</v>
+        <v>971</v>
       </c>
       <c r="C2" t="n">
-        <v>11289</v>
+        <v>3825</v>
       </c>
       <c r="D2" t="n">
-        <v>19903</v>
+        <v>15042</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5184</v>
+        <v>1516</v>
       </c>
       <c r="C3" t="n">
-        <v>12894</v>
+        <v>3027</v>
       </c>
       <c r="D3" t="n">
-        <v>14912</v>
+        <v>14630</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2189</v>
+        <v>2132</v>
       </c>
       <c r="C4" t="n">
-        <v>7584</v>
+        <v>5534</v>
       </c>
       <c r="D4" t="n">
-        <v>7460</v>
+        <v>10907</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1459</v>
+        <v>1739</v>
       </c>
       <c r="C5" t="n">
-        <v>4150</v>
+        <v>6280</v>
       </c>
       <c r="D5" t="n">
-        <v>2354</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>838</v>
       </c>
       <c r="C6" t="n">
-        <v>3356</v>
+        <v>4502</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="C7" t="n">
-        <v>2130</v>
+        <v>1880</v>
       </c>
       <c r="D7" t="n">
-        <v>462</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>665</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4445</v>
+        <v>569</v>
       </c>
       <c r="C2" t="n">
-        <v>5236</v>
+        <v>1826</v>
       </c>
       <c r="D2" t="n">
-        <v>13630</v>
+        <v>11135</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5121</v>
+        <v>1150</v>
       </c>
       <c r="C3" t="n">
-        <v>11076</v>
+        <v>3042</v>
       </c>
       <c r="D3" t="n">
-        <v>14875</v>
+        <v>13843</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2874</v>
+        <v>1759</v>
       </c>
       <c r="C4" t="n">
-        <v>10113</v>
+        <v>4398</v>
       </c>
       <c r="D4" t="n">
-        <v>8377</v>
+        <v>11251</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>1826</v>
       </c>
       <c r="C5" t="n">
-        <v>5574</v>
+        <v>6075</v>
       </c>
       <c r="D5" t="n">
-        <v>2987</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>929</v>
+        <v>1032</v>
       </c>
       <c r="C6" t="n">
-        <v>3828</v>
+        <v>5379</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>2608</v>
+        <v>2779</v>
       </c>
       <c r="D7" t="n">
-        <v>502</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>979</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>415</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4186</v>
+        <v>866</v>
       </c>
       <c r="C2" t="n">
-        <v>8772</v>
+        <v>5919</v>
       </c>
       <c r="D2" t="n">
-        <v>18334</v>
+        <v>11525</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4075</v>
+        <v>769</v>
       </c>
       <c r="C3" t="n">
-        <v>7410</v>
+        <v>2175</v>
       </c>
       <c r="D3" t="n">
-        <v>13706</v>
+        <v>12544</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3263</v>
+        <v>1315</v>
       </c>
       <c r="C4" t="n">
-        <v>10461</v>
+        <v>3684</v>
       </c>
       <c r="D4" t="n">
-        <v>9182</v>
+        <v>11331</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>1664</v>
       </c>
       <c r="C5" t="n">
-        <v>7506</v>
+        <v>5175</v>
       </c>
       <c r="D5" t="n">
-        <v>3724</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1120</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>4546</v>
+        <v>5634</v>
       </c>
       <c r="D6" t="n">
-        <v>1196</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="C7" t="n">
-        <v>3146</v>
+        <v>3926</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>1896</v>
+        <v>1711</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>836</v>
+        <v>628</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2563</v>
+        <v>581</v>
       </c>
       <c r="C2" t="n">
-        <v>4269</v>
+        <v>3077</v>
       </c>
       <c r="D2" t="n">
-        <v>12786</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3959</v>
+        <v>1124</v>
       </c>
       <c r="C3" t="n">
-        <v>7644</v>
+        <v>3390</v>
       </c>
       <c r="D3" t="n">
-        <v>13880</v>
+        <v>13387</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3585</v>
+        <v>2176</v>
       </c>
       <c r="C4" t="n">
-        <v>10310</v>
+        <v>5183</v>
       </c>
       <c r="D4" t="n">
-        <v>9770</v>
+        <v>11796</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1967</v>
+        <v>1274</v>
       </c>
       <c r="C5" t="n">
-        <v>9237</v>
+        <v>7762</v>
       </c>
       <c r="D5" t="n">
-        <v>3932</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>432</v>
       </c>
       <c r="C6" t="n">
-        <v>5479</v>
+        <v>5283</v>
       </c>
       <c r="D6" t="n">
-        <v>1178</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>3335</v>
+        <v>1676</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1376</v>
+        <v>615</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3216</v>
+        <v>346</v>
       </c>
       <c r="C2" t="n">
-        <v>10738</v>
+        <v>1797</v>
       </c>
       <c r="D2" t="n">
-        <v>16141</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2911</v>
+        <v>761</v>
       </c>
       <c r="C3" t="n">
-        <v>5489</v>
+        <v>2850</v>
       </c>
       <c r="D3" t="n">
-        <v>12829</v>
+        <v>11694</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3297</v>
+        <v>1421</v>
       </c>
       <c r="C4" t="n">
-        <v>8966</v>
+        <v>4002</v>
       </c>
       <c r="D4" t="n">
-        <v>10104</v>
+        <v>11235</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2310</v>
+        <v>1186</v>
       </c>
       <c r="C5" t="n">
-        <v>9597</v>
+        <v>5799</v>
       </c>
       <c r="D5" t="n">
-        <v>4653</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>6999</v>
+        <v>5263</v>
       </c>
       <c r="D6" t="n">
-        <v>1544</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>4218</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2074</v>
+        <v>676</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>646</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2456</v>
+        <v>537</v>
       </c>
       <c r="C2" t="n">
-        <v>6526</v>
+        <v>3920</v>
       </c>
       <c r="D2" t="n">
-        <v>11421</v>
+        <v>8012</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2634</v>
+        <v>472</v>
       </c>
       <c r="C3" t="n">
-        <v>6855</v>
+        <v>1969</v>
       </c>
       <c r="D3" t="n">
-        <v>12522</v>
+        <v>9993</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>964</v>
       </c>
       <c r="C4" t="n">
-        <v>7616</v>
+        <v>3304</v>
       </c>
       <c r="D4" t="n">
-        <v>10233</v>
+        <v>10981</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2489</v>
+        <v>1181</v>
       </c>
       <c r="C5" t="n">
-        <v>9547</v>
+        <v>4712</v>
       </c>
       <c r="D5" t="n">
-        <v>5176</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1334</v>
+        <v>715</v>
       </c>
       <c r="C6" t="n">
-        <v>8045</v>
+        <v>5533</v>
       </c>
       <c r="D6" t="n">
-        <v>1794</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>212</v>
       </c>
       <c r="C7" t="n">
-        <v>5132</v>
+        <v>3780</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>2588</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>706</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3710</v>
+        <v>1170</v>
       </c>
       <c r="C2" t="n">
-        <v>5823</v>
+        <v>6240</v>
       </c>
       <c r="D2" t="n">
-        <v>14026</v>
+        <v>15372</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2168</v>
+        <v>414</v>
       </c>
       <c r="C3" t="n">
-        <v>6009</v>
+        <v>2562</v>
       </c>
       <c r="D3" t="n">
-        <v>11617</v>
+        <v>9020</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2450</v>
+        <v>649</v>
       </c>
       <c r="C4" t="n">
-        <v>7150</v>
+        <v>2543</v>
       </c>
       <c r="D4" t="n">
-        <v>10229</v>
+        <v>10371</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2427</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>8606</v>
+        <v>3865</v>
       </c>
       <c r="D5" t="n">
-        <v>5600</v>
+        <v>7141</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1566</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>8528</v>
+        <v>5072</v>
       </c>
       <c r="D6" t="n">
-        <v>2193</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>536</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>6157</v>
+        <v>4620</v>
       </c>
       <c r="D7" t="n">
-        <v>812</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>3459</v>
+        <v>2529</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1277</v>
+        <v>898</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>365</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7163</v>
+        <v>9641</v>
       </c>
       <c r="C2" t="n">
-        <v>11975</v>
+        <v>6953</v>
       </c>
       <c r="D2" t="n">
-        <v>9700</v>
+        <v>14617</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2711</v>
+        <v>1808</v>
       </c>
       <c r="C2" t="n">
-        <v>3447</v>
+        <v>8794</v>
       </c>
       <c r="D2" t="n">
-        <v>10435</v>
+        <v>14243</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2928</v>
+        <v>591</v>
       </c>
       <c r="C3" t="n">
-        <v>6586</v>
+        <v>3725</v>
       </c>
       <c r="D3" t="n">
-        <v>12723</v>
+        <v>9277</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3493</v>
+        <v>476</v>
       </c>
       <c r="C4" t="n">
-        <v>10148</v>
+        <v>2499</v>
       </c>
       <c r="D4" t="n">
-        <v>10378</v>
+        <v>9835</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>786</v>
       </c>
       <c r="C5" t="n">
-        <v>12223</v>
+        <v>3175</v>
       </c>
       <c r="D5" t="n">
-        <v>5128</v>
+        <v>7351</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>495</v>
+        <v>843</v>
       </c>
       <c r="C6" t="n">
-        <v>7538</v>
+        <v>4440</v>
       </c>
       <c r="D6" t="n">
-        <v>1753</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>523</v>
       </c>
       <c r="C7" t="n">
-        <v>3389</v>
+        <v>4817</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>1251</v>
+        <v>3409</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>1544</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>532</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7473</v>
+        <v>8014</v>
       </c>
       <c r="C2" t="n">
-        <v>10744</v>
+        <v>5740</v>
       </c>
       <c r="D2" t="n">
-        <v>14819</v>
+        <v>22508</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3042</v>
+        <v>3104</v>
       </c>
       <c r="C3" t="n">
-        <v>6035</v>
+        <v>2745</v>
       </c>
       <c r="D3" t="n">
-        <v>2268</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5348</v>
+        <v>3892</v>
       </c>
       <c r="C2" t="n">
-        <v>4819</v>
+        <v>3547</v>
       </c>
       <c r="D2" t="n">
-        <v>18483</v>
+        <v>28331</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4318</v>
+        <v>4678</v>
       </c>
       <c r="C3" t="n">
-        <v>7502</v>
+        <v>3907</v>
       </c>
       <c r="D3" t="n">
-        <v>4209</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1356</v>
+        <v>1457</v>
       </c>
       <c r="C4" t="n">
-        <v>3580</v>
+        <v>1761</v>
       </c>
       <c r="D4" t="n">
-        <v>1638</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5524</v>
+        <v>3744</v>
       </c>
       <c r="C2" t="n">
-        <v>5920</v>
+        <v>5567</v>
       </c>
       <c r="D2" t="n">
-        <v>18958</v>
+        <v>33248</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3966</v>
+        <v>3532</v>
       </c>
       <c r="C3" t="n">
-        <v>5260</v>
+        <v>3184</v>
       </c>
       <c r="D3" t="n">
-        <v>6189</v>
+        <v>9243</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2378</v>
+        <v>2693</v>
       </c>
       <c r="C4" t="n">
-        <v>5689</v>
+        <v>3001</v>
       </c>
       <c r="D4" t="n">
-        <v>2081</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>606</v>
+        <v>668</v>
       </c>
       <c r="C5" t="n">
-        <v>2021</v>
+        <v>1098</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6849</v>
+        <v>2683</v>
       </c>
       <c r="C2" t="n">
-        <v>10013</v>
+        <v>3827</v>
       </c>
       <c r="D2" t="n">
-        <v>27222</v>
+        <v>31655</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3857</v>
+        <v>3002</v>
       </c>
       <c r="C3" t="n">
-        <v>4877</v>
+        <v>3880</v>
       </c>
       <c r="D3" t="n">
-        <v>7694</v>
+        <v>12418</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="C4" t="n">
-        <v>5344</v>
+        <v>3042</v>
       </c>
       <c r="D4" t="n">
-        <v>2767</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1210</v>
+        <v>1411</v>
       </c>
       <c r="C5" t="n">
-        <v>3825</v>
+        <v>2116</v>
       </c>
       <c r="D5" t="n">
-        <v>1336</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C6" t="n">
-        <v>1159</v>
+        <v>700</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8194</v>
+        <v>3661</v>
       </c>
       <c r="C2" t="n">
-        <v>6977</v>
+        <v>7228</v>
       </c>
       <c r="D2" t="n">
-        <v>23601</v>
+        <v>31875</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3825</v>
+        <v>2389</v>
       </c>
       <c r="C3" t="n">
-        <v>6149</v>
+        <v>3353</v>
       </c>
       <c r="D3" t="n">
-        <v>9373</v>
+        <v>14467</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2007</v>
+        <v>2437</v>
       </c>
       <c r="C4" t="n">
-        <v>4123</v>
+        <v>3429</v>
       </c>
       <c r="D4" t="n">
-        <v>3055</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1014</v>
+        <v>1774</v>
       </c>
       <c r="C5" t="n">
-        <v>3350</v>
+        <v>2552</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>353</v>
+        <v>743</v>
       </c>
       <c r="C6" t="n">
-        <v>1641</v>
+        <v>1399</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6867</v>
+        <v>4571</v>
       </c>
       <c r="C2" t="n">
-        <v>4084</v>
+        <v>13675</v>
       </c>
       <c r="D2" t="n">
-        <v>23294</v>
+        <v>27747</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4972</v>
+        <v>2428</v>
       </c>
       <c r="C3" t="n">
-        <v>5703</v>
+        <v>4577</v>
       </c>
       <c r="D3" t="n">
-        <v>11073</v>
+        <v>15978</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2549</v>
+        <v>2099</v>
       </c>
       <c r="C4" t="n">
-        <v>5243</v>
+        <v>3319</v>
       </c>
       <c r="D4" t="n">
-        <v>4235</v>
+        <v>6615</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1342</v>
+        <v>1839</v>
       </c>
       <c r="C5" t="n">
-        <v>3725</v>
+        <v>2928</v>
       </c>
       <c r="D5" t="n">
-        <v>1545</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>622</v>
+        <v>1090</v>
       </c>
       <c r="C6" t="n">
-        <v>2572</v>
+        <v>1927</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>1108</v>
+        <v>903</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5281</v>
+        <v>4049</v>
       </c>
       <c r="C2" t="n">
-        <v>8885</v>
+        <v>8423</v>
       </c>
       <c r="D2" t="n">
-        <v>24330</v>
+        <v>21838</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4839</v>
+        <v>3463</v>
       </c>
       <c r="C3" t="n">
-        <v>4216</v>
+        <v>8025</v>
       </c>
       <c r="D3" t="n">
-        <v>12151</v>
+        <v>17539</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3206</v>
+        <v>1699</v>
       </c>
       <c r="C4" t="n">
-        <v>5335</v>
+        <v>4881</v>
       </c>
       <c r="D4" t="n">
-        <v>5312</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1681</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="n">
-        <v>4463</v>
+        <v>1888</v>
       </c>
       <c r="D5" t="n">
-        <v>1988</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>3140</v>
+        <v>884</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>1853</v>
+        <v>378</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>720</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
